--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N80_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N80_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.27715790385471</v>
+        <v>4.595038159376391</v>
       </c>
       <c r="D2" t="n">
-        <v>27.41899131436226</v>
+        <v>4.455586088583867</v>
       </c>
       <c r="E2" t="n">
-        <v>10.17299794875269</v>
+        <v>1.653112166672313</v>
       </c>
       <c r="F2" t="n">
-        <v>9.536210210479474</v>
+        <v>1.549634159202915</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.31943068017378</v>
+        <v>1.67690748552824</v>
       </c>
       <c r="D3" t="n">
-        <v>11.03273922647463</v>
+        <v>1.792820124302128</v>
       </c>
       <c r="E3" t="n">
-        <v>10.17299794875269</v>
+        <v>1.653112166672313</v>
       </c>
       <c r="F3" t="n">
-        <v>9.536210210479474</v>
+        <v>1.549634159202915</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.33360062051443</v>
+        <v>3.791710100833594</v>
       </c>
       <c r="D4" t="n">
-        <v>22.46587403509635</v>
+        <v>3.650704530703157</v>
       </c>
       <c r="E4" t="n">
-        <v>10.17299794875269</v>
+        <v>1.653112166672313</v>
       </c>
       <c r="F4" t="n">
-        <v>9.536210210479474</v>
+        <v>1.549634159202915</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.53577625788436</v>
+        <v>6.099563641906208</v>
       </c>
       <c r="D5" t="n">
-        <v>37.24339626651727</v>
+        <v>6.052051893309056</v>
       </c>
       <c r="E5" t="n">
-        <v>10.17299794875269</v>
+        <v>1.653112166672313</v>
       </c>
       <c r="F5" t="n">
-        <v>9.536210210479474</v>
+        <v>1.549634159202915</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.88172438129248</v>
+        <v>5.180780211960028</v>
       </c>
       <c r="D6" t="n">
-        <v>32.15526964489077</v>
+        <v>5.22523131729475</v>
       </c>
       <c r="E6" t="n">
-        <v>10.17299794875269</v>
+        <v>1.653112166672313</v>
       </c>
       <c r="F6" t="n">
-        <v>9.536210210479474</v>
+        <v>1.549634159202915</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.91260142377212</v>
+        <v>5.348297731362971</v>
       </c>
       <c r="D7" t="n">
-        <v>32.67007480938171</v>
+        <v>5.308887156524528</v>
       </c>
       <c r="E7" t="n">
-        <v>10.17299794875269</v>
+        <v>1.653112166672313</v>
       </c>
       <c r="F7" t="n">
-        <v>9.536210210479474</v>
+        <v>1.549634159202915</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.86092590746563</v>
+        <v>5.339900459963165</v>
       </c>
       <c r="D8" t="n">
-        <v>32.44429156006144</v>
+        <v>5.272197378509984</v>
       </c>
       <c r="E8" t="n">
-        <v>10.17299794875269</v>
+        <v>1.653112166672313</v>
       </c>
       <c r="F8" t="n">
-        <v>9.536210210479474</v>
+        <v>1.549634159202915</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.43401582489135</v>
+        <v>5.433027571544845</v>
       </c>
       <c r="D9" t="n">
-        <v>33.92580940876299</v>
+        <v>5.512944028923987</v>
       </c>
       <c r="E9" t="n">
-        <v>10.17299794875269</v>
+        <v>1.653112166672313</v>
       </c>
       <c r="F9" t="n">
-        <v>9.536210210479474</v>
+        <v>1.549634159202915</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.74067979197189</v>
+        <v>4.182860466195432</v>
       </c>
       <c r="D10" t="n">
-        <v>25.28023891465369</v>
+        <v>4.108038823631224</v>
       </c>
       <c r="E10" t="n">
-        <v>10.17299794875269</v>
+        <v>1.653112166672313</v>
       </c>
       <c r="F10" t="n">
-        <v>9.536210210479474</v>
+        <v>1.549634159202915</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.37181392326877</v>
+        <v>6.560419762531176</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36240942017385</v>
+        <v>5.746391530778251</v>
       </c>
       <c r="E11" t="n">
-        <v>10.17299794875269</v>
+        <v>1.653112166672313</v>
       </c>
       <c r="F11" t="n">
-        <v>9.536210210479474</v>
+        <v>1.549634159202915</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>42.02910050730195</v>
+        <v>6.829728832436568</v>
       </c>
       <c r="D12" t="n">
-        <v>41.55335526699421</v>
+        <v>6.75242023088656</v>
       </c>
       <c r="E12" t="n">
-        <v>10.17299794875269</v>
+        <v>1.653112166672313</v>
       </c>
       <c r="F12" t="n">
-        <v>9.536210210479474</v>
+        <v>1.549634159202915</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.00066933271372</v>
+        <v>5.20010876656598</v>
       </c>
       <c r="D13" t="n">
-        <v>32.30749483404199</v>
+        <v>5.249967910531823</v>
       </c>
       <c r="E13" t="n">
-        <v>10.17299794875269</v>
+        <v>1.653112166672313</v>
       </c>
       <c r="F13" t="n">
-        <v>9.536210210479474</v>
+        <v>1.549634159202915</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>40.11684112793971</v>
+        <v>6.518986683290204</v>
       </c>
       <c r="D14" t="n">
-        <v>36.98986347636336</v>
+        <v>6.010852814909047</v>
       </c>
       <c r="E14" t="n">
-        <v>10.17299794875269</v>
+        <v>1.653112166672313</v>
       </c>
       <c r="F14" t="n">
-        <v>9.536210210479474</v>
+        <v>1.549634159202915</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>11.6219289351535</v>
+        <v>1.888563451962444</v>
       </c>
       <c r="D15" t="n">
-        <v>11.66560674058213</v>
+        <v>1.895661095344597</v>
       </c>
       <c r="E15" t="n">
-        <v>10.17299794875269</v>
+        <v>1.653112166672313</v>
       </c>
       <c r="F15" t="n">
-        <v>9.536210210479474</v>
+        <v>1.549634159202915</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>10.37612166175651</v>
+        <v>1.686119770035434</v>
       </c>
       <c r="D16" t="n">
-        <v>10.53945390735542</v>
+        <v>1.712661259945255</v>
       </c>
       <c r="E16" t="n">
-        <v>10.17299794875269</v>
+        <v>1.653112166672313</v>
       </c>
       <c r="F16" t="n">
-        <v>9.536210210479474</v>
+        <v>1.549634159202915</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>21.3786648092854</v>
+        <v>3.474033031508877</v>
       </c>
       <c r="D17" t="n">
-        <v>21.58530396409145</v>
+        <v>3.507611894164861</v>
       </c>
       <c r="E17" t="n">
-        <v>10.17299794875269</v>
+        <v>1.653112166672313</v>
       </c>
       <c r="F17" t="n">
-        <v>9.536210210479474</v>
+        <v>1.549634159202915</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
